--- a/data_lake/industry/CFM/LPDDR.xlsx
+++ b/data_lake/industry/CFM/LPDDR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/CFM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDBDD4FC-3305-42D8-9C6F-6A23E7584781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1946739-4EB2-424B-8E07-AEF4AA44E48D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18100" yWindow="780" windowWidth="17900" windowHeight="20760" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LPDDR4X 96GB" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -76,36 +76,36 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -142,49 +142,49 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -463,18 +463,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="10"/>
-    <col min="7" max="7" width="11.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -497,7 +497,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -520,7 +520,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -543,7 +543,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -566,7 +566,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -589,7 +589,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -612,7 +612,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -635,7 +635,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -658,7 +658,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -681,7 +681,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -704,7 +704,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -727,7 +727,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -750,7 +750,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -773,7 +773,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -796,7 +796,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -819,7 +819,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -842,7 +842,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -865,7 +865,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -888,7 +888,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -911,7 +911,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -934,7 +934,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -957,7 +957,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -980,7 +980,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="11">
         <v>46035</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="11">
         <v>46042</v>
       </c>
@@ -1095,7 +1095,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -1118,7 +1118,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="11">
         <v>46056</v>
       </c>
@@ -1141,7 +1141,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="11">
         <v>46063</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="11">
         <v>46077</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="11">
         <v>46084</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="11">
         <v>46091</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="11">
         <v>46098</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="11">
         <v>46105</v>
       </c>
@@ -1279,7 +1279,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="11">
         <v>46112</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="11">
         <v>46119</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="11">
         <v>46126</v>
       </c>
@@ -1348,7 +1348,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="11">
         <v>46133</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="11">
         <v>46140</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="11">
         <v>46154</v>
       </c>
@@ -1426,20 +1426,20 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6A21211-5672-4A48-88B4-9571364FB5C8}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="13" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1462,7 +1462,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="11">
         <v>46161</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>46168</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="11">
         <v>46175</v>
       </c>
@@ -1531,7 +1531,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
         <v>46182</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="11">
         <v>46189</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
         <v>46196</v>
       </c>
@@ -1600,7 +1600,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="11">
         <v>46203</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>46210</v>
       </c>
@@ -1646,7 +1646,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="11">
         <v>46217</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
         <v>46224</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="11">
         <v>46231</v>
       </c>
@@ -1715,7 +1715,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="11">
         <v>46238</v>
       </c>
@@ -1735,6 +1735,167 @@
         <v>66</v>
       </c>
       <c r="G13" s="13">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="11">
+        <v>46245</v>
+      </c>
+      <c r="B14" s="11">
+        <v>46245</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="13">
+        <v>56</v>
+      </c>
+      <c r="F14" s="13">
+        <v>66</v>
+      </c>
+      <c r="G14" s="13">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="11">
+        <v>46252</v>
+      </c>
+      <c r="B15" s="11">
+        <v>46252</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="13">
+        <v>56</v>
+      </c>
+      <c r="F15" s="13">
+        <v>66</v>
+      </c>
+      <c r="G15" s="13">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="11">
+        <v>46259</v>
+      </c>
+      <c r="B16" s="11">
+        <v>46259</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="13">
+        <v>56</v>
+      </c>
+      <c r="F16" s="13">
+        <v>66</v>
+      </c>
+      <c r="G16" s="13">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="11">
+        <v>46266</v>
+      </c>
+      <c r="B17" s="11">
+        <v>46266</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="13">
+        <v>56</v>
+      </c>
+      <c r="F17" s="13">
+        <v>66</v>
+      </c>
+      <c r="G17" s="13">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="11">
+        <v>46273</v>
+      </c>
+      <c r="B18" s="11">
+        <v>46273</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="13">
+        <v>56</v>
+      </c>
+      <c r="F18" s="13">
+        <v>66</v>
+      </c>
+      <c r="G18" s="13">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B19" s="11">
+        <v>46280</v>
+      </c>
+      <c r="C19" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="13">
+        <v>56</v>
+      </c>
+      <c r="F19" s="13">
+        <v>66</v>
+      </c>
+      <c r="G19" s="13">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="11">
+        <v>46287</v>
+      </c>
+      <c r="B20" s="11">
+        <v>46287</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="13">
+        <v>56</v>
+      </c>
+      <c r="F20" s="13">
+        <v>66</v>
+      </c>
+      <c r="G20" s="13">
         <v>61</v>
       </c>
     </row>
@@ -1746,19 +1907,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C002ACE-9D35-4283-B798-CF0C9347B851}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.6640625" style="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1781,7 +1942,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -1804,7 +1965,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -1827,7 +1988,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -1850,7 +2011,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -1873,7 +2034,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -1896,7 +2057,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -1919,7 +2080,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -1942,7 +2103,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -1965,7 +2126,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -1988,7 +2149,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -2011,7 +2172,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -2034,7 +2195,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -2057,7 +2218,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -2080,7 +2241,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -2103,7 +2264,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -2126,7 +2287,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -2149,7 +2310,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -2172,7 +2333,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -2195,7 +2356,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -2218,7 +2379,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -2241,7 +2402,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -2264,7 +2425,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -2287,7 +2448,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -2310,7 +2471,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -2333,7 +2494,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="11">
         <v>46035</v>
       </c>
@@ -2356,7 +2517,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="11">
         <v>46042</v>
       </c>
@@ -2379,7 +2540,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -2402,7 +2563,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="11">
         <v>46056</v>
       </c>
@@ -2425,7 +2586,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="11">
         <v>46063</v>
       </c>
@@ -2448,7 +2609,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="11">
         <v>46077</v>
       </c>
@@ -2471,7 +2632,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="11">
         <v>46084</v>
       </c>
@@ -2494,7 +2655,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="11">
         <v>46091</v>
       </c>
@@ -2517,7 +2678,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="11">
         <v>46098</v>
       </c>
@@ -2540,7 +2701,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="11">
         <v>46105</v>
       </c>
@@ -2563,7 +2724,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="11">
         <v>46112</v>
       </c>
@@ -2586,7 +2747,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="11">
         <v>46119</v>
       </c>
@@ -2609,7 +2770,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="11">
         <v>46126</v>
       </c>
@@ -2632,7 +2793,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="11">
         <v>46133</v>
       </c>
@@ -2655,7 +2816,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="11">
         <v>46140</v>
       </c>
@@ -2678,7 +2839,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="11">
         <v>46154</v>
       </c>
@@ -2701,7 +2862,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="11">
         <v>46161</v>
       </c>
@@ -2724,7 +2885,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="11">
         <v>46168</v>
       </c>
@@ -2747,7 +2908,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="11">
         <v>46175</v>
       </c>
@@ -2770,7 +2931,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="11">
         <v>46182</v>
       </c>
@@ -2793,7 +2954,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="11">
         <v>46189</v>
       </c>
@@ -2816,7 +2977,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="11">
         <v>46196</v>
       </c>
@@ -2839,7 +3000,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="11">
         <v>46203</v>
       </c>
@@ -2862,7 +3023,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="11">
         <v>46210</v>
       </c>
@@ -2885,7 +3046,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="11">
         <v>46217</v>
       </c>
@@ -2908,7 +3069,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="11">
         <v>46224</v>
       </c>
@@ -2931,7 +3092,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="11">
         <v>46231</v>
       </c>
@@ -2954,7 +3115,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="11">
         <v>46238</v>
       </c>
@@ -2975,6 +3136,167 @@
       </c>
       <c r="G53" s="10">
         <v>98</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="11">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="11">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="10">
+        <v>96</v>
+      </c>
+      <c r="F54" s="10">
+        <v>100</v>
+      </c>
+      <c r="G54" s="10">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="11">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="11">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="10">
+        <v>96</v>
+      </c>
+      <c r="F55" s="10">
+        <v>100</v>
+      </c>
+      <c r="G55" s="10">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="11">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="11">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="10">
+        <v>94</v>
+      </c>
+      <c r="F56" s="10">
+        <v>98</v>
+      </c>
+      <c r="G56" s="10">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="11">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="11">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="10">
+        <v>94</v>
+      </c>
+      <c r="F57" s="10">
+        <v>98</v>
+      </c>
+      <c r="G57" s="10">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="11">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="11">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="10">
+        <v>91</v>
+      </c>
+      <c r="F58" s="10">
+        <v>95</v>
+      </c>
+      <c r="G58" s="10">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="11">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="10">
+        <v>91</v>
+      </c>
+      <c r="F59" s="10">
+        <v>95</v>
+      </c>
+      <c r="G59" s="10">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="11">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="11">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="10">
+        <v>91</v>
+      </c>
+      <c r="F60" s="10">
+        <v>95</v>
+      </c>
+      <c r="G60" s="10">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2985,20 +3307,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B598A90B-5FE2-4525-ACAE-8E4129C35604}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3021,7 +3343,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -3044,7 +3366,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -3067,7 +3389,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -3090,7 +3412,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -3113,7 +3435,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -3136,7 +3458,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -3159,7 +3481,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -3182,7 +3504,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -3205,7 +3527,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -3228,7 +3550,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -3251,7 +3573,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -3274,7 +3596,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -3297,7 +3619,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -3320,7 +3642,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -3343,7 +3665,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -3366,7 +3688,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -3389,7 +3711,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -3412,7 +3734,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -3435,7 +3757,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -3458,7 +3780,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -3481,7 +3803,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -3504,7 +3826,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -3527,7 +3849,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -3550,7 +3872,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -3573,7 +3895,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="11">
         <v>46035</v>
       </c>
@@ -3596,7 +3918,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="11">
         <v>46042</v>
       </c>
@@ -3619,7 +3941,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -3642,7 +3964,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="11">
         <v>46056</v>
       </c>
@@ -3665,7 +3987,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="11">
         <v>46063</v>
       </c>
@@ -3688,7 +4010,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="11">
         <v>46077</v>
       </c>
@@ -3711,7 +4033,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="11">
         <v>46084</v>
       </c>
@@ -3734,7 +4056,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="11">
         <v>46091</v>
       </c>
@@ -3757,7 +4079,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="11">
         <v>46098</v>
       </c>
@@ -3780,7 +4102,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="11">
         <v>46105</v>
       </c>
@@ -3803,7 +4125,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="11">
         <v>46112</v>
       </c>
@@ -3826,7 +4148,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="11">
         <v>46119</v>
       </c>
@@ -3849,7 +4171,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="11">
         <v>46126</v>
       </c>
@@ -3872,7 +4194,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="11">
         <v>46133</v>
       </c>
@@ -3895,7 +4217,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="11">
         <v>46140</v>
       </c>
@@ -3918,7 +4240,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="11">
         <v>46154</v>
       </c>
@@ -3941,7 +4263,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="11">
         <v>46161</v>
       </c>
@@ -3964,7 +4286,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="11">
         <v>46168</v>
       </c>
@@ -3987,7 +4309,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="11">
         <v>46175</v>
       </c>
@@ -4010,7 +4332,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="11">
         <v>46182</v>
       </c>
@@ -4033,7 +4355,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="11">
         <v>46189</v>
       </c>
@@ -4056,7 +4378,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="11">
         <v>46196</v>
       </c>
@@ -4079,7 +4401,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="11">
         <v>46203</v>
       </c>
@@ -4102,7 +4424,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="11">
         <v>46210</v>
       </c>
@@ -4125,7 +4447,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="11">
         <v>46217</v>
       </c>
@@ -4148,7 +4470,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="11">
         <v>46224</v>
       </c>
@@ -4171,7 +4493,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="11">
         <v>46231</v>
       </c>
@@ -4194,7 +4516,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="11">
         <v>46238</v>
       </c>
@@ -4215,6 +4537,167 @@
       </c>
       <c r="G53" s="10">
         <v>76</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="11">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="11">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="10">
+        <v>71</v>
+      </c>
+      <c r="F54" s="10">
+        <v>78</v>
+      </c>
+      <c r="G54" s="10">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="11">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="11">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="10">
+        <v>71</v>
+      </c>
+      <c r="F55" s="10">
+        <v>78</v>
+      </c>
+      <c r="G55" s="10">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="11">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="11">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="10">
+        <v>69</v>
+      </c>
+      <c r="F56" s="10">
+        <v>76</v>
+      </c>
+      <c r="G56" s="10">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="11">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="11">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="10">
+        <v>69</v>
+      </c>
+      <c r="F57" s="10">
+        <v>76</v>
+      </c>
+      <c r="G57" s="10">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="11">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="11">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="10">
+        <v>68</v>
+      </c>
+      <c r="F58" s="10">
+        <v>75</v>
+      </c>
+      <c r="G58" s="10">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="11">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="10">
+        <v>68</v>
+      </c>
+      <c r="F59" s="10">
+        <v>75</v>
+      </c>
+      <c r="G59" s="10">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="11">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="11">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="10">
+        <v>68</v>
+      </c>
+      <c r="F60" s="10">
+        <v>75</v>
+      </c>
+      <c r="G60" s="10">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -4225,20 +4708,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D1E626F-37CF-4B96-A920-7652799AAE80}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="10"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4261,7 +4744,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -4284,7 +4767,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -4307,7 +4790,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -4330,7 +4813,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -4353,7 +4836,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -4376,7 +4859,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -4399,7 +4882,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -4422,7 +4905,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -4445,7 +4928,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -4468,7 +4951,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -4491,7 +4974,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -4514,7 +4997,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -4537,7 +5020,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -4560,7 +5043,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -4583,7 +5066,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -4606,7 +5089,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -4629,7 +5112,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -4652,7 +5135,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -4675,7 +5158,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -4698,7 +5181,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -4721,7 +5204,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -4744,7 +5227,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -4767,7 +5250,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -4790,7 +5273,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -4813,7 +5296,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="11">
         <v>46035</v>
       </c>
@@ -4836,7 +5319,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="11">
         <v>46042</v>
       </c>
@@ -4859,7 +5342,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -4882,7 +5365,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="11">
         <v>46056</v>
       </c>
@@ -4905,7 +5388,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="11">
         <v>46063</v>
       </c>
@@ -4928,7 +5411,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="11">
         <v>46077</v>
       </c>
@@ -4951,7 +5434,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="11">
         <v>46084</v>
       </c>
@@ -4974,7 +5457,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="11">
         <v>46091</v>
       </c>
@@ -4997,7 +5480,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="11">
         <v>46098</v>
       </c>
@@ -5020,7 +5503,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="11">
         <v>46105</v>
       </c>
@@ -5043,7 +5526,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="11">
         <v>46112</v>
       </c>
@@ -5066,7 +5549,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="11">
         <v>46119</v>
       </c>
@@ -5089,7 +5572,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="11">
         <v>46126</v>
       </c>
@@ -5112,7 +5595,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="11">
         <v>46133</v>
       </c>
@@ -5135,7 +5618,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="11">
         <v>46140</v>
       </c>
@@ -5158,7 +5641,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="11">
         <v>46154</v>
       </c>
@@ -5181,7 +5664,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="11">
         <v>46161</v>
       </c>
@@ -5204,7 +5687,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="11">
         <v>46168</v>
       </c>
@@ -5227,7 +5710,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="11">
         <v>46175</v>
       </c>
@@ -5250,7 +5733,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="11">
         <v>46182</v>
       </c>
@@ -5273,7 +5756,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="11">
         <v>46189</v>
       </c>
@@ -5296,7 +5779,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="11">
         <v>46196</v>
       </c>
@@ -5319,7 +5802,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="11">
         <v>46203</v>
       </c>
@@ -5342,7 +5825,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="11">
         <v>46210</v>
       </c>
@@ -5365,7 +5848,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="11">
         <v>46217</v>
       </c>
@@ -5388,7 +5871,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="11">
         <v>46224</v>
       </c>
@@ -5411,7 +5894,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="11">
         <v>46231</v>
       </c>
@@ -5434,7 +5917,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="11">
         <v>46238</v>
       </c>
@@ -5454,6 +5937,167 @@
         <v>64</v>
       </c>
       <c r="G53" s="10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="11">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="11">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="10">
+        <v>54</v>
+      </c>
+      <c r="F54" s="10">
+        <v>64</v>
+      </c>
+      <c r="G54" s="10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="11">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="11">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="10">
+        <v>54</v>
+      </c>
+      <c r="F55" s="10">
+        <v>64</v>
+      </c>
+      <c r="G55" s="10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="11">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="11">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="10">
+        <v>54</v>
+      </c>
+      <c r="F56" s="10">
+        <v>64</v>
+      </c>
+      <c r="G56" s="10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="11">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="11">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="10">
+        <v>54</v>
+      </c>
+      <c r="F57" s="10">
+        <v>64</v>
+      </c>
+      <c r="G57" s="10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="11">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="11">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="10">
+        <v>54</v>
+      </c>
+      <c r="F58" s="10">
+        <v>64</v>
+      </c>
+      <c r="G58" s="10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="11">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="10">
+        <v>54</v>
+      </c>
+      <c r="F59" s="10">
+        <v>64</v>
+      </c>
+      <c r="G59" s="10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="11">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="11">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="10">
+        <v>54</v>
+      </c>
+      <c r="F60" s="10">
+        <v>64</v>
+      </c>
+      <c r="G60" s="10">
         <v>60</v>
       </c>
     </row>
@@ -5465,20 +6109,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EF2AA72-B42E-4BE9-BF50-F231D4EF8093}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5501,7 +6145,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -5524,7 +6168,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -5547,7 +6191,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -5570,7 +6214,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -5593,7 +6237,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -5616,7 +6260,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -5639,7 +6283,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -5662,7 +6306,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -5685,7 +6329,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -5708,7 +6352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -5731,7 +6375,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -5754,7 +6398,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -5777,7 +6421,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -5800,7 +6444,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -5823,7 +6467,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -5846,7 +6490,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -5869,7 +6513,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -5892,7 +6536,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -5915,7 +6559,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -5938,7 +6582,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -5961,7 +6605,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -5984,7 +6628,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -6007,7 +6651,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -6030,7 +6674,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -6053,7 +6697,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="11">
         <v>46035</v>
       </c>
@@ -6076,7 +6720,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="11">
         <v>46042</v>
       </c>
@@ -6099,7 +6743,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -6122,7 +6766,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="11">
         <v>46056</v>
       </c>
@@ -6145,7 +6789,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="11">
         <v>46063</v>
       </c>
@@ -6168,7 +6812,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="11">
         <v>46077</v>
       </c>
@@ -6191,7 +6835,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="11">
         <v>46084</v>
       </c>
@@ -6214,7 +6858,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="11">
         <v>46091</v>
       </c>
@@ -6237,7 +6881,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="11">
         <v>46098</v>
       </c>
@@ -6260,7 +6904,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="11">
         <v>46105</v>
       </c>
@@ -6283,7 +6927,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="11">
         <v>46112</v>
       </c>
@@ -6306,7 +6950,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="11">
         <v>46119</v>
       </c>
@@ -6329,7 +6973,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="11">
         <v>46126</v>
       </c>
@@ -6352,7 +6996,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="11">
         <v>46133</v>
       </c>
@@ -6375,7 +7019,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="11">
         <v>46140</v>
       </c>
@@ -6398,7 +7042,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="11">
         <v>46154</v>
       </c>
@@ -6421,7 +7065,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="11">
         <v>46161</v>
       </c>
@@ -6444,7 +7088,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="11">
         <v>46168</v>
       </c>
@@ -6467,7 +7111,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="11">
         <v>46175</v>
       </c>
@@ -6490,7 +7134,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="11">
         <v>46182</v>
       </c>
@@ -6513,7 +7157,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="11">
         <v>46189</v>
       </c>
@@ -6536,7 +7180,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="11">
         <v>46196</v>
       </c>
@@ -6559,7 +7203,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="11">
         <v>46203</v>
       </c>
@@ -6582,7 +7226,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="11">
         <v>46210</v>
       </c>
@@ -6605,7 +7249,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="11">
         <v>46217</v>
       </c>
@@ -6628,7 +7272,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="11">
         <v>46224</v>
       </c>
@@ -6651,7 +7295,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="11">
         <v>46231</v>
       </c>
@@ -6674,7 +7318,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="11">
         <v>46238</v>
       </c>
@@ -6694,6 +7338,167 @@
         <v>35</v>
       </c>
       <c r="G53" s="10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="11">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="11">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="10">
+        <v>33.5</v>
+      </c>
+      <c r="F54" s="10">
+        <v>35</v>
+      </c>
+      <c r="G54" s="10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="11">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="11">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="10">
+        <v>33.5</v>
+      </c>
+      <c r="F55" s="10">
+        <v>35</v>
+      </c>
+      <c r="G55" s="10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="11">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="11">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="10">
+        <v>33.5</v>
+      </c>
+      <c r="F56" s="10">
+        <v>35</v>
+      </c>
+      <c r="G56" s="10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="11">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="11">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="10">
+        <v>33.5</v>
+      </c>
+      <c r="F57" s="10">
+        <v>35</v>
+      </c>
+      <c r="G57" s="10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="11">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="11">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="10">
+        <v>33.5</v>
+      </c>
+      <c r="F58" s="10">
+        <v>35</v>
+      </c>
+      <c r="G58" s="10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="11">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="10">
+        <v>33.5</v>
+      </c>
+      <c r="F59" s="10">
+        <v>35</v>
+      </c>
+      <c r="G59" s="10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="11">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="11">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="10">
+        <v>33.5</v>
+      </c>
+      <c r="F60" s="10">
+        <v>35</v>
+      </c>
+      <c r="G60" s="10">
         <v>34</v>
       </c>
     </row>
@@ -6705,20 +7510,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02799ACD-F3A2-408F-864F-69E943B68184}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="13" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6741,7 +7546,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="11">
         <v>46161</v>
       </c>
@@ -6764,7 +7569,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>46168</v>
       </c>
@@ -6787,7 +7592,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="11">
         <v>46175</v>
       </c>
@@ -6810,7 +7615,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
         <v>46182</v>
       </c>
@@ -6833,7 +7638,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="11">
         <v>46189</v>
       </c>
@@ -6856,7 +7661,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
         <v>46196</v>
       </c>
@@ -6879,7 +7684,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="11">
         <v>46203</v>
       </c>
@@ -6902,7 +7707,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>46210</v>
       </c>
@@ -6925,7 +7730,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="11">
         <v>46217</v>
       </c>
@@ -6948,7 +7753,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
         <v>46224</v>
       </c>
@@ -6971,7 +7776,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="11">
         <v>46231</v>
       </c>
@@ -6994,7 +7799,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="11">
         <v>46238</v>
       </c>
@@ -7014,6 +7819,167 @@
         <v>240</v>
       </c>
       <c r="G13" s="13">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="11">
+        <v>46245</v>
+      </c>
+      <c r="B14" s="11">
+        <v>46245</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="13">
+        <v>230</v>
+      </c>
+      <c r="F14" s="13">
+        <v>240</v>
+      </c>
+      <c r="G14" s="13">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="11">
+        <v>46252</v>
+      </c>
+      <c r="B15" s="11">
+        <v>46252</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="13">
+        <v>230</v>
+      </c>
+      <c r="F15" s="13">
+        <v>240</v>
+      </c>
+      <c r="G15" s="13">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="11">
+        <v>46259</v>
+      </c>
+      <c r="B16" s="11">
+        <v>46259</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="13">
+        <v>230</v>
+      </c>
+      <c r="F16" s="13">
+        <v>240</v>
+      </c>
+      <c r="G16" s="13">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="11">
+        <v>46266</v>
+      </c>
+      <c r="B17" s="11">
+        <v>46266</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="13">
+        <v>230</v>
+      </c>
+      <c r="F17" s="13">
+        <v>240</v>
+      </c>
+      <c r="G17" s="13">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="11">
+        <v>46273</v>
+      </c>
+      <c r="B18" s="11">
+        <v>46273</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="13">
+        <v>230</v>
+      </c>
+      <c r="F18" s="13">
+        <v>240</v>
+      </c>
+      <c r="G18" s="13">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B19" s="11">
+        <v>46280</v>
+      </c>
+      <c r="C19" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="13">
+        <v>230</v>
+      </c>
+      <c r="F19" s="13">
+        <v>240</v>
+      </c>
+      <c r="G19" s="13">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="11">
+        <v>46287</v>
+      </c>
+      <c r="B20" s="11">
+        <v>46287</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="13">
+        <v>230</v>
+      </c>
+      <c r="F20" s="13">
+        <v>240</v>
+      </c>
+      <c r="G20" s="13">
         <v>235</v>
       </c>
     </row>
@@ -7025,20 +7991,20 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36ED3A83-EAB3-4813-90B7-C7551CCA3B20}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="13" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7061,7 +8027,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="11">
         <v>46161</v>
       </c>
@@ -7084,7 +8050,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>46168</v>
       </c>
@@ -7107,7 +8073,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="11">
         <v>46175</v>
       </c>
@@ -7130,7 +8096,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
         <v>46182</v>
       </c>
@@ -7153,7 +8119,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="11">
         <v>46189</v>
       </c>
@@ -7176,7 +8142,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
         <v>46196</v>
       </c>
@@ -7199,7 +8165,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="11">
         <v>46203</v>
       </c>
@@ -7222,7 +8188,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>46210</v>
       </c>
@@ -7245,7 +8211,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="11">
         <v>46217</v>
       </c>
@@ -7268,7 +8234,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
         <v>46224</v>
       </c>
@@ -7291,7 +8257,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="11">
         <v>46231</v>
       </c>
@@ -7314,7 +8280,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="11">
         <v>46238</v>
       </c>
@@ -7334,6 +8300,167 @@
         <v>180</v>
       </c>
       <c r="G13" s="13">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="11">
+        <v>46245</v>
+      </c>
+      <c r="B14" s="11">
+        <v>46245</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="13">
+        <v>170</v>
+      </c>
+      <c r="F14" s="13">
+        <v>180</v>
+      </c>
+      <c r="G14" s="13">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="11">
+        <v>46252</v>
+      </c>
+      <c r="B15" s="11">
+        <v>46252</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="13">
+        <v>170</v>
+      </c>
+      <c r="F15" s="13">
+        <v>180</v>
+      </c>
+      <c r="G15" s="13">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="11">
+        <v>46259</v>
+      </c>
+      <c r="B16" s="11">
+        <v>46259</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="13">
+        <v>170</v>
+      </c>
+      <c r="F16" s="13">
+        <v>180</v>
+      </c>
+      <c r="G16" s="13">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="11">
+        <v>46266</v>
+      </c>
+      <c r="B17" s="11">
+        <v>46266</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="13">
+        <v>170</v>
+      </c>
+      <c r="F17" s="13">
+        <v>180</v>
+      </c>
+      <c r="G17" s="13">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="11">
+        <v>46273</v>
+      </c>
+      <c r="B18" s="11">
+        <v>46273</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="13">
+        <v>170</v>
+      </c>
+      <c r="F18" s="13">
+        <v>180</v>
+      </c>
+      <c r="G18" s="13">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B19" s="11">
+        <v>46280</v>
+      </c>
+      <c r="C19" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="13">
+        <v>170</v>
+      </c>
+      <c r="F19" s="13">
+        <v>180</v>
+      </c>
+      <c r="G19" s="13">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="11">
+        <v>46287</v>
+      </c>
+      <c r="B20" s="11">
+        <v>46287</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="13">
+        <v>170</v>
+      </c>
+      <c r="F20" s="13">
+        <v>180</v>
+      </c>
+      <c r="G20" s="13">
         <v>175</v>
       </c>
     </row>
@@ -7345,20 +8472,20 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A48A7DD7-D740-4DE5-96FE-EC5DB0F7F7D6}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="13" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7381,7 +8508,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="11">
         <v>46161</v>
       </c>
@@ -7404,7 +8531,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>46168</v>
       </c>
@@ -7427,7 +8554,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="11">
         <v>46175</v>
       </c>
@@ -7450,7 +8577,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
         <v>46182</v>
       </c>
@@ -7473,7 +8600,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="11">
         <v>46189</v>
       </c>
@@ -7496,7 +8623,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
         <v>46196</v>
       </c>
@@ -7519,7 +8646,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="11">
         <v>46203</v>
       </c>
@@ -7542,7 +8669,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>46210</v>
       </c>
@@ -7565,7 +8692,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="11">
         <v>46217</v>
       </c>
@@ -7588,7 +8715,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
         <v>46224</v>
       </c>
@@ -7611,7 +8738,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="11">
         <v>46231</v>
       </c>
@@ -7634,7 +8761,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="11">
         <v>46238</v>
       </c>
@@ -7654,6 +8781,167 @@
         <v>116</v>
       </c>
       <c r="G13" s="13">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="11">
+        <v>46245</v>
+      </c>
+      <c r="B14" s="11">
+        <v>46245</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="13">
+        <v>112</v>
+      </c>
+      <c r="F14" s="13">
+        <v>116</v>
+      </c>
+      <c r="G14" s="13">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="11">
+        <v>46252</v>
+      </c>
+      <c r="B15" s="11">
+        <v>46252</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="13">
+        <v>112</v>
+      </c>
+      <c r="F15" s="13">
+        <v>116</v>
+      </c>
+      <c r="G15" s="13">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="11">
+        <v>46259</v>
+      </c>
+      <c r="B16" s="11">
+        <v>46259</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="13">
+        <v>112</v>
+      </c>
+      <c r="F16" s="13">
+        <v>116</v>
+      </c>
+      <c r="G16" s="13">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="11">
+        <v>46266</v>
+      </c>
+      <c r="B17" s="11">
+        <v>46266</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="13">
+        <v>112</v>
+      </c>
+      <c r="F17" s="13">
+        <v>116</v>
+      </c>
+      <c r="G17" s="13">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="11">
+        <v>46273</v>
+      </c>
+      <c r="B18" s="11">
+        <v>46273</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="13">
+        <v>112</v>
+      </c>
+      <c r="F18" s="13">
+        <v>116</v>
+      </c>
+      <c r="G18" s="13">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B19" s="11">
+        <v>46280</v>
+      </c>
+      <c r="C19" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="13">
+        <v>112</v>
+      </c>
+      <c r="F19" s="13">
+        <v>116</v>
+      </c>
+      <c r="G19" s="13">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="11">
+        <v>46287</v>
+      </c>
+      <c r="B20" s="11">
+        <v>46287</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="13">
+        <v>112</v>
+      </c>
+      <c r="F20" s="13">
+        <v>116</v>
+      </c>
+      <c r="G20" s="13">
         <v>114</v>
       </c>
     </row>
@@ -7665,20 +8953,20 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFDE94D2-A563-4C21-8A9D-D80E69343286}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="13" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7701,7 +8989,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="11">
         <v>46161</v>
       </c>
@@ -7724,7 +9012,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>46168</v>
       </c>
@@ -7747,7 +9035,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="11">
         <v>46175</v>
       </c>
@@ -7770,7 +9058,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
         <v>46182</v>
       </c>
@@ -7793,7 +9081,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="11">
         <v>46189</v>
       </c>
@@ -7816,7 +9104,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
         <v>46196</v>
       </c>
@@ -7839,7 +9127,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="11">
         <v>46203</v>
       </c>
@@ -7862,7 +9150,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>46210</v>
       </c>
@@ -7885,7 +9173,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="11">
         <v>46217</v>
       </c>
@@ -7908,7 +9196,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
         <v>46224</v>
       </c>
@@ -7931,7 +9219,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="11">
         <v>46231</v>
       </c>
@@ -7954,7 +9242,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="11">
         <v>46238</v>
       </c>
@@ -7974,6 +9262,167 @@
         <v>91</v>
       </c>
       <c r="G13" s="13">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="11">
+        <v>46245</v>
+      </c>
+      <c r="B14" s="11">
+        <v>46245</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="13">
+        <v>83</v>
+      </c>
+      <c r="F14" s="13">
+        <v>91</v>
+      </c>
+      <c r="G14" s="13">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="11">
+        <v>46252</v>
+      </c>
+      <c r="B15" s="11">
+        <v>46252</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="13">
+        <v>83</v>
+      </c>
+      <c r="F15" s="13">
+        <v>91</v>
+      </c>
+      <c r="G15" s="13">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="11">
+        <v>46259</v>
+      </c>
+      <c r="B16" s="11">
+        <v>46259</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="13">
+        <v>83</v>
+      </c>
+      <c r="F16" s="13">
+        <v>91</v>
+      </c>
+      <c r="G16" s="13">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="11">
+        <v>46266</v>
+      </c>
+      <c r="B17" s="11">
+        <v>46266</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="13">
+        <v>83</v>
+      </c>
+      <c r="F17" s="13">
+        <v>91</v>
+      </c>
+      <c r="G17" s="13">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="11">
+        <v>46273</v>
+      </c>
+      <c r="B18" s="11">
+        <v>46273</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="13">
+        <v>83</v>
+      </c>
+      <c r="F18" s="13">
+        <v>91</v>
+      </c>
+      <c r="G18" s="13">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B19" s="11">
+        <v>46280</v>
+      </c>
+      <c r="C19" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="13">
+        <v>83</v>
+      </c>
+      <c r="F19" s="13">
+        <v>91</v>
+      </c>
+      <c r="G19" s="13">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="11">
+        <v>46287</v>
+      </c>
+      <c r="B20" s="11">
+        <v>46287</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="13">
+        <v>83</v>
+      </c>
+      <c r="F20" s="13">
+        <v>91</v>
+      </c>
+      <c r="G20" s="13">
         <v>88</v>
       </c>
     </row>
